--- a/dev_Python/1. 업무/2. 수질환경/3. Excel to Word 변환 장비대장/20261002_장비대장 html 프로그램 개발 자료/20261002_장비관리대장 통합.xlsx
+++ b/dev_Python/1. 업무/2. 수질환경/3. Excel to Word 변환 장비대장/20261002_장비대장 html 프로그램 개발 자료/20261002_장비관리대장 통합.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waste\Downloads\20261002_장비대장 html 프로그램 개발 자료\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\learning\dev_Python\1. 업무\2. 수질환경\3. Excel to Word 변환 장비대장\20261002_장비대장 html 프로그램 개발 자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7832C8B-D92D-4759-BF97-8BDE413EDD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3C4936-8672-4F61-B407-F24797D71AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="503" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="503" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="장비대장" sheetId="3" r:id="rId1"/>
@@ -18,15 +18,29 @@
     <sheet name="장비구성" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">장비구성!$A$1:$E$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">장비구성!$A$1:$E$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">장비대장!$A$1:$U$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="599">
   <si>
     <t>관리번호</t>
   </si>
@@ -1607,36 +1621,18 @@
     <t>ea</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Delivery flow system</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>Detergent level sensor</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Support for beakers (50 or more beakers available)</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Washing Insert</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Injection nozzle (56 or more nozzels available)</t>
   </si>
   <si>
@@ -1649,16 +1645,7 @@
     <t>Data Processing Unit</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Power CORD SET,PHP-206S+PHS-301 2.4M (KOR)</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>12</t>
   </si>
   <si>
     <t>Type1 P-10, V-3.5mL Quartz Cell</t>
@@ -1765,12 +1752,6 @@
     <t>BOD 인큐베이터(Serial No. 12112UC0001)</t>
   </si>
   <si>
-    <t>물벼룩배양기(Serial No.</t>
-  </si>
-  <si>
-    <t>04-장비-89</t>
-  </si>
-  <si>
     <t>Thermal Desorber System</t>
   </si>
   <si>
@@ -1822,24 +1803,15 @@
     <t>Main Body</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>로터 및 시료용기 세트 (24HVT50)</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>로터 및 시료용기 세트(16HF100)</t>
   </si>
   <si>
     <t>2차 Ultra 370</t>
   </si>
   <si>
-    <t>04-장비-74-1</t>
-  </si>
-  <si>
     <t>1차 Basic 360</t>
   </si>
   <si>
@@ -1853,66 +1825,6 @@
   </si>
   <si>
     <t>Headspace(Tekmar HT3)</t>
-  </si>
-  <si>
-    <t>Control System(PC)</t>
-  </si>
-  <si>
-    <t>04-장비-73</t>
-  </si>
-  <si>
-    <t>Autosampler</t>
-  </si>
-  <si>
-    <t>전처리 장치</t>
-  </si>
-  <si>
-    <t>Operation Software</t>
-  </si>
-  <si>
-    <t>04-장비-72</t>
-  </si>
-  <si>
-    <t>Dual NDIR Dectector</t>
-  </si>
-  <si>
-    <t>UV/Persulfate, Dual Oxidation</t>
-  </si>
-  <si>
-    <t>Air Compressor</t>
-  </si>
-  <si>
-    <t>04-장비-71</t>
-  </si>
-  <si>
-    <t>Vapor Generation System</t>
-  </si>
-  <si>
-    <t>Flame Automation  System</t>
-  </si>
-  <si>
-    <t>04-장비-69</t>
-  </si>
-  <si>
-    <t>시약주입장치(AASU-2000)</t>
-  </si>
-  <si>
-    <t>Auto Sampler(HSU-2020)</t>
-  </si>
-  <si>
-    <t>전처리 장치(D2BX-02)</t>
-  </si>
-  <si>
-    <t>순수제조기, 전자저울, 조도계, 현미경)</t>
-  </si>
-  <si>
-    <t>04-장비-64</t>
-  </si>
-  <si>
-    <t>(pH meter, DO meter, 냉장고, 노트북,</t>
-  </si>
-  <si>
-    <t>물벼룩배양 및 독성측정기외 8종</t>
   </si>
   <si>
     <t>방진판(석판)</t>
@@ -1928,35 +1840,6 @@
   <si>
     <t>분동 50 g (지시값등급 50 g/E2)
 기물번호 : 18929995</t>
-  </si>
-  <si>
-    <t>Air Compressor(Precisely Compressor)
-Perkin Elmer</t>
-  </si>
-  <si>
-    <t>04-장비-43</t>
-  </si>
-  <si>
-    <t>Recirculation Water Cooling sys.
-(Cooling Sys. 5000 PE) perkin Elmer</t>
-  </si>
-  <si>
-    <t>UPS(NPS2000) 한도전원</t>
-  </si>
-  <si>
-    <t>AUTOSAMPLER</t>
-  </si>
-  <si>
-    <t>04-장비-42</t>
-  </si>
-  <si>
-    <t>2대/set</t>
-  </si>
-  <si>
-    <t>MIR 552</t>
-  </si>
-  <si>
-    <t>04-장비-07~08</t>
   </si>
   <si>
     <t>관리번호</t>
@@ -2029,84 +1912,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">  1. 1370 × 680 × 1450
-  2. 용량 : 1350 L
-  3. 외장 : Galvanized steel powder coating
-  4. 내장 : ABS, PE
-  5. 연구목적용 시료를 (4 ± 2) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로 보관하는 용도로 사용되는 핀 없는
-    응축기를 이용한 무제상 냉장고</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">  - 법적냉동능력 6.09 RT
   - 냉방 정격능력 29,000 W
   - 난방 정격능력 33,000 W
   - 최대운전전류 32.0A
   - 옥내용 113kg(옥외 실외기 별도)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - Forced convection type
- - Temperature Range : Ambient to 260℃(±0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> at 140</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)
- - 137L, SUS304
- - 60W blower fan
- - Over heat protector, Power breaker
- - Power(AC220V, 60Hz) 2Kw</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2138,86 +1948,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>TOC Analyzer: multi N/C 3100
-multiWin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ⓡ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> PC software
-Autosampler: AS vario ER autosampler with additional needle cleaning
-Sample rack: 72 positions for AS vario ER
-Protective cover for AS vario and AS vario ER
-Desktop PC, Laser Printer
-CO2 Free Gas Generator
-Ultira Sonic Bath(40 Khz)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SCION SQ Quadrupole Mass Spectrometer
 456-GC Gas Chromatograph
 CP-8400 Liquid AutoSampler
 PerkinElmer TurboMatrix 40 Mid-range Headspace AutoSampler</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Temp Range: (-5 ~ 70)℃
-Temp Accuracy: ±0.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> at 25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-Temp Control: 10 Step Temp Program Controller
-Demension(In): (600 x 600 x 1,200) mm
-Demension(Out): (750 x 880 x 1,790) mm
-Safety Device: High &amp; Low Temp Protector
-Capacity: 432 L  - 전원: 220V, 7A, 1.5kW</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2256,36 +1990,6 @@
   <si>
     <t>시료 농축기, 후드시설, 가스 공급장치 기능을 모두 갖춘 통합시료 농축 시스템
 Evatros T.C.S(농축기), Evatros G(가스공급장치)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Isocratic dual piston pump Flow rate: 0.001 - 20.00 mL/min
-Isocratic dual piston pump Pressure rage: 0 – 35 MPa
-Injection valve Injection loop: 20 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="161"/>
-      </rPr>
-      <t>μ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>L
-Anion suppressor Type: Micro-packed bed
-Conductivity Detector: DSP
-Autosampler Sample tube capacity: 148 ea
-Eluent production Flow rate: 0~35 MPa</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2333,45 +2037,99 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> - 제어방식: 마이크로컨트롤러 기반 자동 세척 시스템
+    <t>연번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04-장비-기타1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정제수 제조장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04-장비-74, 기체크로마토그래프와 함께 증류수장치 도입됨 한 세트로 묶임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정제수 제조 장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  1. 1370 × 680 × 1450
+  2. 용량 : 1350 L
+  3. 외장 : Galvanized steel powder coating
+  4. 내장 : ABS, PE
+  5. 연구목적용 시료를 (4 ± 2) ℃로 보관하는 용도로 사용되는 핀 없는
+    응축기를 이용한 무제상 냉장고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Forced convection type
+ - Temperature Range : Ambient to 260℃(±0.3℃ at 140℃)
+ - 137L, SUS304
+ - 60W blower fan
+ - Over heat protector, Power breaker
+ - Power(AC220V, 60Hz) 2Kw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOC Analyzer: multi N/C 3100
+multiWinⓇ PC software
+Autosampler: AS vario ER autosampler with additional needle cleaning
+Sample rack: 72 positions for AS vario ER
+Protective cover for AS vario and AS vario ER
+Desktop PC, Laser Printer
+CO2 Free Gas Generator
+Ultira Sonic Bath(40 Khz)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temp Range: (-5 ~ 70)℃
+Temp Accuracy: ±0.2℃ at 25℃
+Temp Control: 10 Step Temp Program Controller
+Demension(In): (600 x 600 x 1,200) mm
+Demension(Out): (750 x 880 x 1,790) mm
+Safety Device: High &amp; Low Temp Protector
+Capacity: 432 L  - 전원: 220V, 7A, 1.5kW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Isocratic dual piston pump Flow rate: 0.001 - 20.00 mL/min
+Isocratic dual piston pump Pressure rage: 0 – 35 MPa
+Injection valve Injection loop: 20 μL
+Anion suppressor Type: Micro-packed bed
+Conductivity Detector: DSP
+Autosampler Sample tube capacity: 148 ea
+Eluent production Flow rate: 0~35 MPa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 제어방식: 마이크로컨트롤러 기반 자동 세척 시스템
  - 탱크 재질: AISI 316L 스테인리스
  - 세척 성능: 세척 펌프 유량 600 L/min
- - 온도 범위: 실온 ~ 95℃ (정확도 ±0.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)
+ - 온도 범위: 실온 ~ 95℃ (정확도 ±0.1℃)
  - 가열 방식: 전기 가열식 (13 kW)
  - 건조 시스템: 열풍 건조 방식 (건조 팬 220 m³/h)
  - 내부 크기: 550 × 620 × 685 mm
  - 전원/설비: 온수·냉수·탈이온수 3라인 급수</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>연번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>단위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2382,7 +2140,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2409,12 +2167,6 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2445,25 +2197,16 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
-      <charset val="161"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2474,7 +2217,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2512,14 +2255,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2535,56 +2288,71 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2805,3784 +2573,3862 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AC48"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:AC49"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" customWidth="1"/>
-    <col min="8" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.85546875" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="7" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" customWidth="1"/>
-    <col min="20" max="20" width="35" customWidth="1"/>
-    <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="38" customWidth="1"/>
-    <col min="23" max="23" width="18.5703125" customWidth="1"/>
-    <col min="24" max="24" width="36.42578125" customWidth="1"/>
-    <col min="25" max="25" width="68.5703125" customWidth="1"/>
-    <col min="26" max="26" width="21.5703125" customWidth="1"/>
-    <col min="27" max="27" width="9.140625" customWidth="1"/>
-    <col min="28" max="29" width="68.5703125" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" style="7" customWidth="1"/>
+    <col min="8" max="10" width="17.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.85546875" style="7" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="23" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="7" customWidth="1"/>
+    <col min="20" max="20" width="35" style="7" customWidth="1"/>
+    <col min="21" max="21" width="18" style="7" customWidth="1"/>
+    <col min="22" max="22" width="38" style="7" customWidth="1"/>
+    <col min="23" max="23" width="18.5703125" style="7" customWidth="1"/>
+    <col min="24" max="24" width="36.42578125" style="7" customWidth="1"/>
+    <col min="25" max="25" width="68.5703125" style="7" customWidth="1"/>
+    <col min="26" max="26" width="21.5703125" style="7" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" style="7" customWidth="1"/>
+    <col min="28" max="29" width="68.5703125" style="7" customWidth="1"/>
+    <col min="30" max="16384" width="14.42578125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:29" s="19" customFormat="1">
+      <c r="A1" s="18" t="s">
         <v>318</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="14" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="W1" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="X1" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="Y1" s="15" t="s">
+      <c r="Y1" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="Z1" s="15" t="s">
+      <c r="Z1" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="AA1" s="15" t="s">
+      <c r="AA1" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="AB1" s="15" t="s">
+      <c r="AB1" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="AC1" s="15" t="s">
+      <c r="AC1" s="16" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:29">
-      <c r="A2" s="16">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="4">
         <v>34720</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4">
         <v>34720</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="17">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="2">
         <v>1995</v>
       </c>
-      <c r="O2" s="17">
-        <v>1</v>
-      </c>
-      <c r="P2" s="20">
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="5">
         <v>1086000</v>
       </c>
-      <c r="Q2" s="20">
+      <c r="Q2" s="5">
         <f t="shared" ref="Q2:Q48" si="0">ROUND(P2/1000,0)</f>
         <v>1086</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="S2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="U2" s="18" t="s">
+      <c r="U2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="V2" s="22" t="s">
+      <c r="V2" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22" t="s">
+      <c r="W2" s="17"/>
+      <c r="X2" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="Z2" s="22" t="s">
+      <c r="Z2" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="AA2" s="22" t="s">
+      <c r="AA2" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
     </row>
     <row r="3" spans="1:29">
-      <c r="A3" s="16">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="4">
         <v>34720</v>
       </c>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4">
         <v>34720</v>
       </c>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="17">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="2">
         <v>1995</v>
       </c>
-      <c r="O3" s="17">
-        <v>1</v>
-      </c>
-      <c r="P3" s="20">
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
         <v>1086000</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="5">
         <f t="shared" si="0"/>
         <v>1086</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="R3" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S3" s="18" t="s">
+      <c r="S3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="T3" s="18" t="s">
+      <c r="T3" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="U3" s="18" t="s">
+      <c r="U3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="22" t="s">
+      <c r="V3" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22" t="s">
+      <c r="W3" s="17"/>
+      <c r="X3" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="Y3" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="Z3" s="22" t="s">
+      <c r="Z3" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="AA3" s="22" t="s">
+      <c r="AA3" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
     </row>
     <row r="4" spans="1:29">
-      <c r="A4" s="16">
+      <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="4">
         <v>38169</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="4">
         <v>38169</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="4">
         <v>38169</v>
       </c>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="17">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="2">
         <v>2004</v>
       </c>
-      <c r="O4" s="17">
-        <v>1</v>
-      </c>
-      <c r="P4" s="20">
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
         <v>9278000</v>
       </c>
-      <c r="Q4" s="20">
+      <c r="Q4" s="5">
         <f t="shared" si="0"/>
         <v>9278</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="R4" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="22" t="s">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="W4" s="22" t="s">
+      <c r="W4" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="X4" s="22" t="s">
+      <c r="X4" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="Y4" s="22" t="s">
+      <c r="Y4" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="AA4" s="22" t="s">
+      <c r="AA4" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB4" s="22"/>
-      <c r="AC4" s="22"/>
-    </row>
-    <row r="5" spans="1:29" ht="40.5">
-      <c r="A5" s="16">
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="4">
         <v>38169</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="4">
         <v>38169</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="4">
         <v>38169</v>
       </c>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="17">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="2">
         <v>2004</v>
       </c>
-      <c r="O5" s="17">
-        <v>1</v>
-      </c>
-      <c r="P5" s="20">
+      <c r="O5" s="2">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
         <v>6313000</v>
       </c>
-      <c r="Q5" s="20">
+      <c r="Q5" s="5">
         <f t="shared" si="0"/>
         <v>6313</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="R5" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S5" s="18" t="s">
+      <c r="S5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="22" t="s">
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="W5" s="22" t="s">
+      <c r="W5" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="X5" s="22" t="s">
+      <c r="X5" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="Y5" s="22" t="s">
+      <c r="Y5" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="Z5" s="22" t="s">
+      <c r="Z5" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="AA5" s="22" t="s">
+      <c r="AA5" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB5" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="AC5" s="22"/>
+      <c r="AB5" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="AC5" s="17"/>
     </row>
     <row r="6" spans="1:29">
-      <c r="A6" s="16">
+      <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="4">
         <v>38560</v>
       </c>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19">
+      <c r="I6" s="4"/>
+      <c r="J6" s="4">
         <v>38560</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="17">
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="2">
         <v>2005</v>
       </c>
-      <c r="O6" s="17">
-        <v>1</v>
-      </c>
-      <c r="P6" s="20">
+      <c r="O6" s="2">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
         <v>1470000</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="Q6" s="5">
         <f t="shared" si="0"/>
         <v>1470</v>
       </c>
-      <c r="R6" s="21" t="s">
+      <c r="R6" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S6" s="18" t="s">
+      <c r="S6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="22" t="s">
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22" t="s">
+      <c r="W6" s="17"/>
+      <c r="X6" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="Y6" s="22" t="s">
+      <c r="Y6" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="Z6" s="22" t="s">
+      <c r="Z6" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="AA6" s="22" t="s">
+      <c r="AA6" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-    </row>
-    <row r="7" spans="1:29" ht="40.5">
-      <c r="A7" s="16">
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="20">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="4">
         <v>38560</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="4">
         <v>38560</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="4">
         <v>38560</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="17">
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="2">
         <v>2005</v>
       </c>
-      <c r="O7" s="17">
-        <v>1</v>
-      </c>
-      <c r="P7" s="20">
+      <c r="O7" s="2">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
         <v>5821000</v>
       </c>
-      <c r="Q7" s="20">
+      <c r="Q7" s="5">
         <f t="shared" si="0"/>
         <v>5821</v>
       </c>
-      <c r="R7" s="21" t="s">
+      <c r="R7" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S7" s="18" t="s">
+      <c r="S7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="T7" s="18" t="s">
+      <c r="T7" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="U7" s="18"/>
-      <c r="V7" s="22" t="s">
+      <c r="U7" s="3"/>
+      <c r="V7" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="W7" s="22" t="s">
+      <c r="W7" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="X7" s="22" t="s">
+      <c r="X7" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="Y7" s="22" t="s">
+      <c r="Y7" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="Z7" s="22" t="s">
+      <c r="Z7" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="AA7" s="22" t="s">
+      <c r="AA7" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-    </row>
-    <row r="8" spans="1:29" ht="27">
-      <c r="A8" s="16">
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="17"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="20">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="4">
         <v>39737</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="4">
         <v>39737</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="4">
         <v>39737</v>
       </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="17">
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="2">
         <v>2008</v>
       </c>
-      <c r="O8" s="17">
-        <v>1</v>
-      </c>
-      <c r="P8" s="20">
+      <c r="O8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5">
         <v>6645000</v>
       </c>
-      <c r="Q8" s="20">
+      <c r="Q8" s="5">
         <f t="shared" si="0"/>
         <v>6645</v>
       </c>
-      <c r="R8" s="21" t="s">
+      <c r="R8" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S8" s="18" t="s">
+      <c r="S8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18" t="s">
+      <c r="T8" s="3"/>
+      <c r="U8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="V8" s="22" t="s">
+      <c r="V8" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="W8" s="22" t="s">
+      <c r="W8" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="X8" s="22" t="s">
+      <c r="X8" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="Y8" s="22" t="s">
+      <c r="Y8" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="Z8" s="22" t="s">
+      <c r="Z8" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="AA8" s="22" t="s">
+      <c r="AA8" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22" t="s">
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="54">
-      <c r="A9" s="16">
+    <row r="9" spans="1:29">
+      <c r="A9" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="4">
         <v>39737</v>
       </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
         <v>39737</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="17">
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="2">
         <v>2008</v>
       </c>
-      <c r="O9" s="17">
-        <v>1</v>
-      </c>
-      <c r="P9" s="20">
+      <c r="O9" s="2">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5">
         <v>3410000</v>
       </c>
-      <c r="Q9" s="20">
+      <c r="Q9" s="5">
         <f t="shared" si="0"/>
         <v>3410</v>
       </c>
-      <c r="R9" s="21" t="s">
+      <c r="R9" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S9" s="18" t="s">
+      <c r="S9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="22" t="s">
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="W9" s="22" t="s">
+      <c r="W9" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="X9" s="22" t="s">
+      <c r="X9" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="Y9" s="22" t="s">
+      <c r="Y9" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="Z9" s="22" t="s">
+      <c r="Z9" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="AA9" s="22" t="s">
+      <c r="AA9" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB9" s="22" t="s">
+      <c r="AB9" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="AC9" s="22" t="s">
+      <c r="AC9" s="17" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="67.5">
-      <c r="A10" s="16">
+    <row r="10" spans="1:29">
+      <c r="A10" s="20">
         <v>9</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="4">
         <v>39737</v>
       </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19">
+      <c r="I10" s="4"/>
+      <c r="J10" s="4">
         <v>39737</v>
       </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="17">
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="2">
         <v>2008</v>
       </c>
-      <c r="O10" s="17">
-        <v>1</v>
-      </c>
-      <c r="P10" s="20">
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5">
         <v>1178000</v>
       </c>
-      <c r="Q10" s="20">
+      <c r="Q10" s="5">
         <f t="shared" si="0"/>
         <v>1178</v>
       </c>
-      <c r="R10" s="21" t="s">
+      <c r="R10" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S10" s="18" t="s">
+      <c r="S10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="22" t="s">
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="W10" s="22" t="s">
+      <c r="W10" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="X10" s="22" t="s">
+      <c r="X10" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="Y10" s="22" t="s">
+      <c r="Y10" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="Z10" s="22" t="s">
+      <c r="Z10" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="AA10" s="22" t="s">
+      <c r="AA10" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB10" s="22" t="s">
+      <c r="AB10" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="AC10" s="22" t="s">
+      <c r="AC10" s="17" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:29">
-      <c r="A11" s="16">
+      <c r="A11" s="20">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="4">
         <v>39737</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="4">
         <v>39737</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="4">
         <v>39737</v>
       </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="19">
+      <c r="K11" s="4"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="4">
         <v>43822</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="2">
         <v>2008</v>
       </c>
-      <c r="O11" s="17">
-        <v>1</v>
-      </c>
-      <c r="P11" s="20">
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+      <c r="P11" s="5">
         <v>5050000</v>
       </c>
-      <c r="Q11" s="20">
+      <c r="Q11" s="5">
         <f t="shared" si="0"/>
         <v>5050</v>
       </c>
-      <c r="R11" s="21" t="s">
+      <c r="R11" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S11" s="18" t="s">
+      <c r="S11" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="T11" s="18" t="s">
+      <c r="T11" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="U11" s="18"/>
-      <c r="V11" s="22" t="s">
+      <c r="U11" s="3"/>
+      <c r="V11" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="W11" s="22" t="s">
+      <c r="W11" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="X11" s="22" t="s">
+      <c r="X11" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="Y11" s="22" t="s">
+      <c r="Y11" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="Z11" s="22" t="s">
+      <c r="Z11" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="AA11" s="22" t="s">
+      <c r="AA11" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB11" s="22" t="s">
-        <v>605</v>
-      </c>
-      <c r="AC11" s="22" t="s">
+      <c r="AB11" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="AC11" s="17" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="121.5">
-      <c r="A12" s="16">
+    <row r="12" spans="1:29">
+      <c r="A12" s="20">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="4">
         <v>39899</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="4">
         <v>39903</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="4">
         <v>39903</v>
       </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19">
+      <c r="K12" s="4"/>
+      <c r="L12" s="4">
         <v>44562</v>
       </c>
-      <c r="M12" s="19"/>
-      <c r="N12" s="17">
+      <c r="M12" s="4"/>
+      <c r="N12" s="2">
         <v>2009</v>
       </c>
-      <c r="O12" s="17">
-        <v>1</v>
-      </c>
-      <c r="P12" s="20">
+      <c r="O12" s="2">
+        <v>1</v>
+      </c>
+      <c r="P12" s="5">
         <v>10750300</v>
       </c>
-      <c r="Q12" s="20">
+      <c r="Q12" s="5">
         <f t="shared" si="0"/>
         <v>10750</v>
       </c>
-      <c r="R12" s="21" t="s">
+      <c r="R12" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S12" s="18" t="s">
+      <c r="S12" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="T12" s="18" t="s">
+      <c r="T12" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="U12" s="18"/>
-      <c r="V12" s="22" t="s">
+      <c r="U12" s="3"/>
+      <c r="V12" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22" t="s">
+      <c r="W12" s="17"/>
+      <c r="X12" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="Y12" s="22" t="s">
+      <c r="Y12" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="Z12" s="22" t="s">
+      <c r="Z12" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="AA12" s="22" t="s">
+      <c r="AA12" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB12" s="22" t="s">
-        <v>606</v>
-      </c>
-      <c r="AC12" s="22" t="s">
+      <c r="AB12" s="17" t="s">
+        <v>563</v>
+      </c>
+      <c r="AC12" s="17" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="94.5">
-      <c r="A13" s="16">
+    <row r="13" spans="1:29">
+      <c r="A13" s="20">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="4">
         <v>39899</v>
       </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
         <v>39899</v>
       </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19">
+      <c r="K13" s="4"/>
+      <c r="L13" s="4">
         <v>44562</v>
       </c>
-      <c r="M13" s="19"/>
-      <c r="N13" s="17">
+      <c r="M13" s="4"/>
+      <c r="N13" s="2">
         <v>2009</v>
       </c>
-      <c r="O13" s="17">
-        <v>1</v>
-      </c>
-      <c r="P13" s="20">
+      <c r="O13" s="2">
+        <v>1</v>
+      </c>
+      <c r="P13" s="5">
         <v>2500000</v>
       </c>
-      <c r="Q13" s="20">
+      <c r="Q13" s="5">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="R13" s="21" t="s">
+      <c r="R13" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S13" s="18" t="s">
+      <c r="S13" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="T13" s="18" t="s">
+      <c r="T13" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="U13" s="18"/>
-      <c r="V13" s="22" t="s">
+      <c r="U13" s="3"/>
+      <c r="V13" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="W13" s="22" t="s">
+      <c r="W13" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="X13" s="22" t="s">
+      <c r="X13" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="Y13" s="22" t="s">
+      <c r="Y13" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="Z13" s="22" t="s">
+      <c r="Z13" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="AA13" s="22" t="s">
+      <c r="AA13" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB13" s="22" t="s">
+      <c r="AB13" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="AC13" s="22"/>
-    </row>
-    <row r="14" spans="1:29" ht="27">
-      <c r="A14" s="16">
+      <c r="AC13" s="17"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="20">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="4">
         <v>41813</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="4">
         <v>41813</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="4">
         <v>41813</v>
       </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="17">
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="2">
         <v>2014</v>
       </c>
-      <c r="O14" s="17">
-        <v>1</v>
-      </c>
-      <c r="P14" s="20">
+      <c r="O14" s="2">
+        <v>1</v>
+      </c>
+      <c r="P14" s="5">
         <v>152682060</v>
       </c>
-      <c r="Q14" s="20">
+      <c r="Q14" s="5">
         <f t="shared" si="0"/>
         <v>152682</v>
       </c>
-      <c r="R14" s="21" t="s">
+      <c r="R14" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S14" s="18" t="s">
+      <c r="S14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="T14" s="18" t="s">
+      <c r="T14" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="U14" s="18" t="s">
+      <c r="U14" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="V14" s="22" t="s">
+      <c r="V14" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="W14" s="22" t="s">
+      <c r="W14" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="X14" s="22" t="s">
+      <c r="X14" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="Y14" s="22" t="s">
+      <c r="Y14" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="Z14" s="22" t="s">
+      <c r="Z14" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="AA14" s="22" t="s">
+      <c r="AA14" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB14" s="22" t="s">
-        <v>607</v>
-      </c>
-      <c r="AC14" s="22"/>
-    </row>
-    <row r="15" spans="1:29" ht="121.5">
-      <c r="A15" s="16">
+      <c r="AB14" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="AC14" s="17"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="20">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="4">
         <v>42558</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="4">
         <v>42544</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="4">
         <v>42544</v>
       </c>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="17">
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="2">
         <v>2016</v>
       </c>
-      <c r="O15" s="17">
-        <v>1</v>
-      </c>
-      <c r="P15" s="20">
+      <c r="O15" s="2">
+        <v>1</v>
+      </c>
+      <c r="P15" s="5">
         <v>37010300</v>
       </c>
-      <c r="Q15" s="20">
+      <c r="Q15" s="5">
         <f t="shared" si="0"/>
         <v>37010</v>
       </c>
-      <c r="R15" s="21" t="s">
+      <c r="R15" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S15" s="18" t="s">
+      <c r="S15" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="22" t="s">
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22" t="s">
+      <c r="W15" s="17"/>
+      <c r="X15" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="Y15" s="22" t="s">
+      <c r="Y15" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="Z15" s="22" t="s">
+      <c r="Z15" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="AA15" s="22" t="s">
+      <c r="AA15" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB15" s="22" t="s">
-        <v>608</v>
-      </c>
-      <c r="AC15" s="22" t="s">
+      <c r="AB15" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="AC15" s="17" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="202.5">
-      <c r="A16" s="16">
+    <row r="16" spans="1:29">
+      <c r="A16" s="20">
         <v>15</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="4">
         <v>42647</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="4">
         <v>42598</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="4">
         <v>42598</v>
       </c>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="17">
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="2">
         <v>2016</v>
       </c>
-      <c r="O16" s="17">
-        <v>1</v>
-      </c>
-      <c r="P16" s="20">
+      <c r="O16" s="2">
+        <v>1</v>
+      </c>
+      <c r="P16" s="5">
         <v>59438210</v>
       </c>
-      <c r="Q16" s="20">
+      <c r="Q16" s="5">
         <f t="shared" si="0"/>
         <v>59438</v>
       </c>
-      <c r="R16" s="21" t="s">
+      <c r="R16" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S16" s="18" t="s">
+      <c r="S16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="22" t="s">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="W16" s="22" t="s">
+      <c r="W16" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="X16" s="22" t="s">
+      <c r="X16" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="Y16" s="22" t="s">
+      <c r="Y16" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="Z16" s="22" t="s">
+      <c r="Z16" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="AA16" s="22" t="s">
+      <c r="AA16" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB16" s="22" t="s">
+      <c r="AB16" s="17" t="s">
         <v>471</v>
       </c>
-      <c r="AC16" s="22" t="s">
+      <c r="AC16" s="17" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="81">
-      <c r="A17" s="16">
+    <row r="17" spans="1:29">
+      <c r="A17" s="20">
         <v>16</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="4">
         <v>42760</v>
       </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
         <v>42760</v>
       </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="17">
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="2">
         <v>2017</v>
       </c>
-      <c r="O17" s="17">
-        <v>1</v>
-      </c>
-      <c r="P17" s="20">
+      <c r="O17" s="2">
+        <v>1</v>
+      </c>
+      <c r="P17" s="5">
         <v>1925000</v>
       </c>
-      <c r="Q17" s="20">
+      <c r="Q17" s="5">
         <f t="shared" si="0"/>
         <v>1925</v>
       </c>
-      <c r="R17" s="21" t="s">
+      <c r="R17" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S17" s="18" t="s">
+      <c r="S17" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="22" t="s">
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22" t="s">
+      <c r="W17" s="17"/>
+      <c r="X17" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="Y17" s="22" t="s">
+      <c r="Y17" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="Z17" s="22" t="s">
+      <c r="Z17" s="17" t="s">
         <v>398</v>
       </c>
-      <c r="AA17" s="22" t="s">
+      <c r="AA17" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB17" s="22" t="s">
-        <v>609</v>
-      </c>
-      <c r="AC17" s="22" t="s">
+      <c r="AB17" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="AC17" s="17" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="67.5">
-      <c r="A18" s="16">
+    <row r="18" spans="1:29">
+      <c r="A18" s="20">
         <v>17</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="4">
         <v>42781</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19">
+      <c r="I18" s="4"/>
+      <c r="J18" s="4">
         <v>42781</v>
       </c>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="17">
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="2">
         <v>2017</v>
       </c>
-      <c r="O18" s="17">
-        <v>1</v>
-      </c>
-      <c r="P18" s="20">
+      <c r="O18" s="2">
+        <v>1</v>
+      </c>
+      <c r="P18" s="5">
         <v>1430000</v>
       </c>
-      <c r="Q18" s="20">
+      <c r="Q18" s="5">
         <f t="shared" si="0"/>
         <v>1430</v>
       </c>
-      <c r="R18" s="21" t="s">
+      <c r="R18" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S18" s="18" t="s">
+      <c r="S18" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="22" t="s">
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="W18" s="22" t="s">
+      <c r="W18" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="X18" s="22" t="s">
+      <c r="X18" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="Y18" s="22" t="s">
+      <c r="Y18" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="Z18" s="22" t="s">
+      <c r="Z18" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="AA18" s="22" t="s">
+      <c r="AA18" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB18" s="22" t="s">
-        <v>610</v>
-      </c>
-      <c r="AC18" s="22" t="s">
+      <c r="AB18" s="17" t="s">
+        <v>567</v>
+      </c>
+      <c r="AC18" s="17" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="67.5">
-      <c r="A19" s="16">
+    <row r="19" spans="1:29">
+      <c r="A19" s="20">
         <v>18</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="4">
         <v>42781</v>
       </c>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19">
+      <c r="I19" s="4"/>
+      <c r="J19" s="4">
         <v>42781</v>
       </c>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="17">
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="2">
         <v>2017</v>
       </c>
-      <c r="O19" s="17">
-        <v>1</v>
-      </c>
-      <c r="P19" s="20">
+      <c r="O19" s="2">
+        <v>1</v>
+      </c>
+      <c r="P19" s="5">
         <v>1430000</v>
       </c>
-      <c r="Q19" s="20">
+      <c r="Q19" s="5">
         <f t="shared" si="0"/>
         <v>1430</v>
       </c>
-      <c r="R19" s="21" t="s">
+      <c r="R19" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S19" s="18" t="s">
+      <c r="S19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="22" t="s">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="W19" s="22" t="s">
+      <c r="W19" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="X19" s="22" t="s">
+      <c r="X19" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="Y19" s="22" t="s">
+      <c r="Y19" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="Z19" s="22" t="s">
+      <c r="Z19" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="AA19" s="22" t="s">
+      <c r="AA19" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB19" s="22" t="s">
-        <v>610</v>
-      </c>
-      <c r="AC19" s="22" t="s">
+      <c r="AB19" s="17" t="s">
+        <v>567</v>
+      </c>
+      <c r="AC19" s="17" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="94.5">
-      <c r="A20" s="16">
+    <row r="20" spans="1:29">
+      <c r="A20" s="20">
         <v>19</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="4">
         <v>42837</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="4">
         <v>42838</v>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="4">
         <v>42838</v>
       </c>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="17">
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="2">
         <v>2017</v>
       </c>
-      <c r="O20" s="17">
-        <v>1</v>
-      </c>
-      <c r="P20" s="20">
+      <c r="O20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20" s="5">
         <v>12166000</v>
       </c>
-      <c r="Q20" s="20">
+      <c r="Q20" s="5">
         <f t="shared" si="0"/>
         <v>12166</v>
       </c>
-      <c r="R20" s="21" t="s">
+      <c r="R20" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S20" s="18" t="s">
+      <c r="S20" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="T20" s="18" t="s">
+      <c r="T20" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="U20" s="18"/>
-      <c r="V20" s="22" t="s">
+      <c r="U20" s="3"/>
+      <c r="V20" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="W20" s="22" t="s">
+      <c r="W20" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="X20" s="22" t="s">
+      <c r="X20" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="Y20" s="22" t="s">
+      <c r="Y20" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="Z20" s="22" t="s">
+      <c r="Z20" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="AA20" s="22" t="s">
+      <c r="AA20" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB20" s="22" t="s">
-        <v>611</v>
-      </c>
-      <c r="AC20" s="22" t="s">
+      <c r="AB20" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="AC20" s="17" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="81.75">
-      <c r="A21" s="16">
+    <row r="21" spans="1:29">
+      <c r="A21" s="20">
         <v>20</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="4">
         <v>43129</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="4">
         <v>43129</v>
       </c>
-      <c r="J21" s="19">
+      <c r="J21" s="4">
         <v>43129</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="17">
+      <c r="K21" s="4"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="2">
         <v>2018</v>
       </c>
-      <c r="O21" s="17">
-        <v>1</v>
-      </c>
-      <c r="P21" s="20">
+      <c r="O21" s="2">
+        <v>1</v>
+      </c>
+      <c r="P21" s="5">
         <v>7739240</v>
       </c>
-      <c r="Q21" s="20">
+      <c r="Q21" s="5">
         <f t="shared" si="0"/>
         <v>7739</v>
       </c>
-      <c r="R21" s="21" t="s">
+      <c r="R21" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S21" s="18" t="s">
+      <c r="S21" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="22" t="s">
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="W21" s="22" t="s">
+      <c r="W21" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="X21" s="22" t="s">
+      <c r="X21" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="Y21" s="22" t="s">
+      <c r="Y21" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="Z21" s="22" t="s">
+      <c r="Z21" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="AA21" s="22" t="s">
+      <c r="AA21" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB21" s="22" t="s">
-        <v>612</v>
-      </c>
-      <c r="AC21" s="22" t="s">
+      <c r="AB21" s="17" t="s">
+        <v>592</v>
+      </c>
+      <c r="AC21" s="17" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="67.5">
-      <c r="A22" s="16">
+    <row r="22" spans="1:29">
+      <c r="A22" s="20">
         <v>21</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="4">
         <v>43164</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="4">
         <v>43164</v>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="4">
         <v>43164</v>
       </c>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="17">
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="2">
         <v>2018</v>
       </c>
-      <c r="O22" s="17">
-        <v>1</v>
-      </c>
-      <c r="P22" s="20">
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+      <c r="P22" s="5">
         <v>5573930</v>
       </c>
-      <c r="Q22" s="20">
+      <c r="Q22" s="5">
         <f t="shared" si="0"/>
         <v>5574</v>
       </c>
-      <c r="R22" s="21" t="s">
+      <c r="R22" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S22" s="18" t="s">
+      <c r="S22" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="22" t="s">
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="W22" s="22"/>
-      <c r="X22" s="22" t="s">
+      <c r="W22" s="17"/>
+      <c r="X22" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="Y22" s="22" t="s">
+      <c r="Y22" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="Z22" s="22" t="s">
+      <c r="Z22" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="AA22" s="22" t="s">
+      <c r="AA22" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB22" s="22" t="s">
-        <v>613</v>
-      </c>
-      <c r="AC22" s="22" t="s">
+      <c r="AB22" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="AC22" s="17" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="81.75">
-      <c r="A23" s="16">
+    <row r="23" spans="1:29">
+      <c r="A23" s="20">
         <v>22</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="4">
         <v>43522</v>
       </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19">
+      <c r="I23" s="4"/>
+      <c r="J23" s="4">
         <v>43522</v>
       </c>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="17">
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="2">
         <v>2019</v>
       </c>
-      <c r="O23" s="17">
-        <v>1</v>
-      </c>
-      <c r="P23" s="20">
+      <c r="O23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23" s="5">
         <v>1870000</v>
       </c>
-      <c r="Q23" s="20">
+      <c r="Q23" s="5">
         <f t="shared" si="0"/>
         <v>1870</v>
       </c>
-      <c r="R23" s="21" t="s">
+      <c r="R23" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S23" s="18" t="s">
+      <c r="S23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="T23" s="18" t="s">
+      <c r="T23" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="U23" s="18"/>
-      <c r="V23" s="22" t="s">
+      <c r="U23" s="3"/>
+      <c r="V23" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22" t="s">
+      <c r="W23" s="17"/>
+      <c r="X23" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="Y23" s="22" t="s">
+      <c r="Y23" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="Z23" s="22" t="s">
+      <c r="Z23" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="AA23" s="22" t="s">
+      <c r="AA23" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB23" s="22" t="s">
-        <v>614</v>
-      </c>
-      <c r="AC23" s="22"/>
-    </row>
-    <row r="24" spans="1:29" ht="108">
-      <c r="A24" s="16">
+      <c r="AB23" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="AC23" s="17"/>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="A24" s="20">
         <v>23</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="4">
         <v>43656</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="4">
         <v>43656</v>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="4">
         <v>43656</v>
       </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="17">
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="2">
         <v>2019</v>
       </c>
-      <c r="O24" s="17">
-        <v>1</v>
-      </c>
-      <c r="P24" s="20">
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+      <c r="P24" s="5">
         <v>79971570</v>
       </c>
-      <c r="Q24" s="20">
+      <c r="Q24" s="5">
         <f t="shared" si="0"/>
         <v>79972</v>
       </c>
-      <c r="R24" s="21" t="s">
+      <c r="R24" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S24" s="18" t="s">
+      <c r="S24" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="T24" s="18" t="s">
+      <c r="T24" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="U24" s="18"/>
-      <c r="V24" s="22" t="s">
+      <c r="U24" s="3"/>
+      <c r="V24" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="W24" s="22" t="s">
+      <c r="W24" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="X24" s="22" t="s">
+      <c r="X24" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="Y24" s="22" t="s">
+      <c r="Y24" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="Z24" s="22" t="s">
+      <c r="Z24" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="AA24" s="22" t="s">
+      <c r="AA24" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB24" s="22" t="s">
-        <v>615</v>
-      </c>
-      <c r="AC24" s="22"/>
-    </row>
-    <row r="25" spans="1:29" ht="67.5">
-      <c r="A25" s="16">
+      <c r="AB24" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="AC24" s="17"/>
+    </row>
+    <row r="25" spans="1:29">
+      <c r="A25" s="20">
         <v>24</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="4">
         <v>43067</v>
       </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19">
+      <c r="I25" s="4"/>
+      <c r="J25" s="4">
         <v>43067</v>
       </c>
-      <c r="K25" s="19"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="19">
+      <c r="K25" s="4"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="4">
         <v>44562</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="2">
         <v>2017</v>
       </c>
-      <c r="O25" s="17">
-        <v>1</v>
-      </c>
-      <c r="P25" s="20">
+      <c r="O25" s="2">
+        <v>1</v>
+      </c>
+      <c r="P25" s="5">
         <v>2990900</v>
       </c>
-      <c r="Q25" s="20">
+      <c r="Q25" s="5">
         <f t="shared" si="0"/>
         <v>2991</v>
       </c>
-      <c r="R25" s="21" t="s">
+      <c r="R25" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S25" s="18" t="s">
+      <c r="S25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="T25" s="18" t="s">
+      <c r="T25" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="U25" s="18" t="s">
+      <c r="U25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="V25" s="22" t="s">
+      <c r="V25" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="W25" s="22" t="s">
+      <c r="W25" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="X25" s="22" t="s">
+      <c r="X25" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="Y25" s="22" t="s">
+      <c r="Y25" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="Z25" s="22" t="s">
+      <c r="Z25" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="AA25" s="22" t="s">
+      <c r="AA25" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB25" s="22" t="s">
-        <v>616</v>
-      </c>
-      <c r="AC25" s="22"/>
-    </row>
-    <row r="26" spans="1:29" ht="94.5">
-      <c r="A26" s="16">
+      <c r="AB25" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="AC25" s="17"/>
+    </row>
+    <row r="26" spans="1:29">
+      <c r="A26" s="20">
         <v>25</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="4">
         <v>43964</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="4">
         <v>43964</v>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="4">
         <v>43964</v>
       </c>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="17">
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="2">
         <v>2020</v>
       </c>
-      <c r="O26" s="17">
-        <v>1</v>
-      </c>
-      <c r="P26" s="20">
+      <c r="O26" s="2">
+        <v>1</v>
+      </c>
+      <c r="P26" s="5">
         <v>11990000</v>
       </c>
-      <c r="Q26" s="20">
+      <c r="Q26" s="5">
         <f t="shared" si="0"/>
         <v>11990</v>
       </c>
-      <c r="R26" s="21" t="s">
+      <c r="R26" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S26" s="18" t="s">
+      <c r="S26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="T26" s="18" t="s">
+      <c r="T26" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="U26" s="18"/>
-      <c r="V26" s="22" t="s">
+      <c r="U26" s="3"/>
+      <c r="V26" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="W26" s="22"/>
-      <c r="X26" s="22" t="s">
+      <c r="W26" s="17"/>
+      <c r="X26" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="Y26" s="22" t="s">
+      <c r="Y26" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="Z26" s="22" t="s">
+      <c r="Z26" s="17" t="s">
         <v>418</v>
       </c>
-      <c r="AA26" s="22" t="s">
+      <c r="AA26" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB26" s="22" t="s">
-        <v>617</v>
-      </c>
-      <c r="AC26" s="22" t="s">
+      <c r="AB26" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="AC26" s="17" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="121.5">
-      <c r="A27" s="16">
+    <row r="27" spans="1:29">
+      <c r="A27" s="20">
         <v>26</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="4">
         <v>43971</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="4">
         <v>43971</v>
       </c>
-      <c r="J27" s="19">
+      <c r="J27" s="4">
         <v>43971</v>
       </c>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="17">
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="2">
         <v>2020</v>
       </c>
-      <c r="O27" s="17">
-        <v>1</v>
-      </c>
-      <c r="P27" s="20">
+      <c r="O27" s="2">
+        <v>1</v>
+      </c>
+      <c r="P27" s="5">
         <v>25400000</v>
       </c>
-      <c r="Q27" s="20">
+      <c r="Q27" s="5">
         <f t="shared" si="0"/>
         <v>25400</v>
       </c>
-      <c r="R27" s="21" t="s">
+      <c r="R27" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S27" s="18" t="s">
+      <c r="S27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="T27" s="18" t="s">
+      <c r="T27" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="U27" s="18"/>
-      <c r="V27" s="22" t="s">
+      <c r="U27" s="3"/>
+      <c r="V27" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="W27" s="22" t="s">
+      <c r="W27" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="X27" s="22" t="s">
+      <c r="X27" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="Y27" s="22" t="s">
+      <c r="Y27" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="Z27" s="22" t="s">
+      <c r="Z27" s="17" t="s">
         <v>421</v>
       </c>
-      <c r="AA27" s="22" t="s">
+      <c r="AA27" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB27" s="22" t="s">
+      <c r="AB27" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="AC27" s="22"/>
-    </row>
-    <row r="28" spans="1:29" ht="108.75">
-      <c r="A28" s="16">
+      <c r="AC27" s="17"/>
+    </row>
+    <row r="28" spans="1:29">
+      <c r="A28" s="20">
         <v>27</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="4">
         <v>43991</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="4">
         <v>43991</v>
       </c>
-      <c r="J28" s="19">
+      <c r="J28" s="4">
         <v>43991</v>
       </c>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="17">
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="2">
         <v>2020</v>
       </c>
-      <c r="O28" s="17">
-        <v>1</v>
-      </c>
-      <c r="P28" s="20">
+      <c r="O28" s="2">
+        <v>1</v>
+      </c>
+      <c r="P28" s="5">
         <v>54097410</v>
       </c>
-      <c r="Q28" s="20">
+      <c r="Q28" s="5">
         <f t="shared" si="0"/>
         <v>54097</v>
       </c>
-      <c r="R28" s="21" t="s">
+      <c r="R28" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S28" s="18" t="s">
+      <c r="S28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="T28" s="18" t="s">
+      <c r="T28" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="U28" s="18"/>
-      <c r="V28" s="22" t="s">
+      <c r="U28" s="3"/>
+      <c r="V28" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="W28" s="22" t="s">
+      <c r="W28" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="X28" s="22" t="s">
+      <c r="X28" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="Y28" s="22" t="s">
+      <c r="Y28" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22" t="s">
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB28" s="22" t="s">
-        <v>618</v>
-      </c>
-      <c r="AC28" s="22" t="s">
+      <c r="AB28" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="AC28" s="17" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="54">
-      <c r="A29" s="16">
+    <row r="29" spans="1:29">
+      <c r="A29" s="20">
         <v>28</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="4">
         <v>43994</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="4">
         <v>43994</v>
       </c>
-      <c r="J29" s="19">
+      <c r="J29" s="4">
         <v>43994</v>
       </c>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="17">
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="2">
         <v>2020</v>
       </c>
-      <c r="O29" s="17">
-        <v>1</v>
-      </c>
-      <c r="P29" s="20">
+      <c r="O29" s="2">
+        <v>1</v>
+      </c>
+      <c r="P29" s="5">
         <v>140549890</v>
       </c>
-      <c r="Q29" s="20">
+      <c r="Q29" s="5">
         <f t="shared" si="0"/>
         <v>140550</v>
       </c>
-      <c r="R29" s="21" t="s">
+      <c r="R29" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S29" s="18" t="s">
+      <c r="S29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="T29" s="18" t="s">
+      <c r="T29" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="U29" s="18" t="s">
+      <c r="U29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="V29" s="22" t="s">
+      <c r="V29" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="W29" s="22"/>
-      <c r="X29" s="22" t="s">
+      <c r="W29" s="17"/>
+      <c r="X29" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="Y29" s="22" t="s">
+      <c r="Y29" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="Z29" s="22" t="s">
+      <c r="Z29" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="AA29" s="22" t="s">
+      <c r="AA29" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB29" s="22" t="s">
-        <v>619</v>
-      </c>
-      <c r="AC29" s="22"/>
-    </row>
-    <row r="30" spans="1:29" ht="95.25">
-      <c r="A30" s="16">
+      <c r="AB29" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="AC29" s="17"/>
+    </row>
+    <row r="30" spans="1:29">
+      <c r="A30" s="20">
         <v>29</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="4">
         <v>44280</v>
       </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19">
+      <c r="I30" s="4"/>
+      <c r="J30" s="4">
         <v>44280</v>
       </c>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="17">
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="2">
         <v>2021</v>
       </c>
-      <c r="O30" s="17">
-        <v>1</v>
-      </c>
-      <c r="P30" s="20">
+      <c r="O30" s="2">
+        <v>1</v>
+      </c>
+      <c r="P30" s="5">
         <v>4840000</v>
       </c>
-      <c r="Q30" s="20">
+      <c r="Q30" s="5">
         <f t="shared" si="0"/>
         <v>4840</v>
       </c>
-      <c r="R30" s="21" t="s">
+      <c r="R30" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S30" s="18" t="s">
+      <c r="S30" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="T30" s="18" t="s">
+      <c r="T30" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="U30" s="18" t="s">
+      <c r="U30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="V30" s="22" t="s">
+      <c r="V30" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="W30" s="22" t="s">
+      <c r="W30" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="X30" s="22" t="s">
+      <c r="X30" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="Y30" s="22" t="s">
+      <c r="Y30" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="Z30" s="22" t="s">
+      <c r="Z30" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="AA30" s="22" t="s">
+      <c r="AA30" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB30" s="22" t="s">
-        <v>620</v>
-      </c>
-      <c r="AC30" s="22"/>
-    </row>
-    <row r="31" spans="1:29" ht="95.25">
-      <c r="A31" s="16">
+      <c r="AB30" s="17" t="s">
+        <v>595</v>
+      </c>
+      <c r="AC30" s="17"/>
+    </row>
+    <row r="31" spans="1:29">
+      <c r="A31" s="20">
         <v>30</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="G31" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="4">
         <v>44280</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19">
+      <c r="I31" s="4"/>
+      <c r="J31" s="4">
         <v>44280</v>
       </c>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="17">
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="2">
         <v>2021</v>
       </c>
-      <c r="O31" s="17">
-        <v>1</v>
-      </c>
-      <c r="P31" s="20">
+      <c r="O31" s="2">
+        <v>1</v>
+      </c>
+      <c r="P31" s="5">
         <v>4840000</v>
       </c>
-      <c r="Q31" s="20">
+      <c r="Q31" s="5">
         <f t="shared" si="0"/>
         <v>4840</v>
       </c>
-      <c r="R31" s="21" t="s">
+      <c r="R31" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S31" s="18" t="s">
+      <c r="S31" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="22" t="s">
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="W31" s="22" t="s">
+      <c r="W31" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="X31" s="22" t="s">
+      <c r="X31" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="Y31" s="22" t="s">
+      <c r="Y31" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="Z31" s="22" t="s">
+      <c r="Z31" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="AA31" s="22" t="s">
+      <c r="AA31" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB31" s="22" t="s">
-        <v>620</v>
-      </c>
-      <c r="AC31" s="22"/>
-    </row>
-    <row r="32" spans="1:29" ht="81">
-      <c r="A32" s="16">
+      <c r="AB31" s="17" t="s">
+        <v>595</v>
+      </c>
+      <c r="AC31" s="17"/>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" s="20">
         <v>31</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="4">
         <v>44435</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="4">
         <v>44435</v>
       </c>
-      <c r="J32" s="19">
+      <c r="J32" s="4">
         <v>44435</v>
       </c>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="17">
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="2">
         <v>2021</v>
       </c>
-      <c r="O32" s="17">
-        <v>1</v>
-      </c>
-      <c r="P32" s="20">
+      <c r="O32" s="2">
+        <v>1</v>
+      </c>
+      <c r="P32" s="5">
         <v>114658070</v>
       </c>
-      <c r="Q32" s="20">
+      <c r="Q32" s="5">
         <f t="shared" si="0"/>
         <v>114658</v>
       </c>
-      <c r="R32" s="21" t="s">
+      <c r="R32" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S32" s="18" t="s">
+      <c r="S32" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="22" t="s">
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="W32" s="22" t="s">
+      <c r="W32" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="X32" s="22" t="s">
+      <c r="X32" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="Y32" s="22" t="s">
+      <c r="Y32" s="17" t="s">
         <v>430</v>
       </c>
-      <c r="Z32" s="22" t="s">
+      <c r="Z32" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="AA32" s="22" t="s">
+      <c r="AA32" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB32" s="22" t="s">
-        <v>622</v>
-      </c>
-      <c r="AC32" s="22"/>
-    </row>
-    <row r="33" spans="1:29" ht="94.5">
-      <c r="A33" s="16">
+      <c r="AB32" s="17" t="s">
+        <v>575</v>
+      </c>
+      <c r="AC32" s="17"/>
+    </row>
+    <row r="33" spans="1:29">
+      <c r="A33" s="20">
         <v>32</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="4">
         <v>44453</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="4">
         <v>44453</v>
       </c>
-      <c r="J33" s="19">
+      <c r="J33" s="4">
         <v>44453</v>
       </c>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="17">
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="2">
         <v>2021</v>
       </c>
-      <c r="O33" s="17">
-        <v>1</v>
-      </c>
-      <c r="P33" s="20">
+      <c r="O33" s="2">
+        <v>1</v>
+      </c>
+      <c r="P33" s="5">
         <v>354917360</v>
       </c>
-      <c r="Q33" s="20">
+      <c r="Q33" s="5">
         <f t="shared" si="0"/>
         <v>354917</v>
       </c>
-      <c r="R33" s="21" t="s">
+      <c r="R33" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S33" s="18" t="s">
+      <c r="S33" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="T33" s="18"/>
-      <c r="U33" s="18" t="s">
+      <c r="T33" s="3"/>
+      <c r="U33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="V33" s="22" t="s">
+      <c r="V33" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="W33" s="22" t="s">
+      <c r="W33" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="X33" s="22" t="s">
+      <c r="X33" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="Y33" s="22" t="s">
+      <c r="Y33" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="Z33" s="22" t="s">
+      <c r="Z33" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="AA33" s="22" t="s">
+      <c r="AA33" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB33" s="22" t="s">
-        <v>621</v>
-      </c>
-      <c r="AC33" s="22"/>
-    </row>
-    <row r="34" spans="1:29" ht="27">
-      <c r="A34" s="16">
+      <c r="AB33" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="AC33" s="17"/>
+    </row>
+    <row r="34" spans="1:29">
+      <c r="A34" s="20">
         <v>33</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="4">
         <v>44753</v>
       </c>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19">
+      <c r="I34" s="4"/>
+      <c r="J34" s="4">
         <v>44753</v>
       </c>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="17">
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="2">
         <v>2022</v>
       </c>
-      <c r="O34" s="17">
-        <v>1</v>
-      </c>
-      <c r="P34" s="20">
+      <c r="O34" s="2">
+        <v>1</v>
+      </c>
+      <c r="P34" s="5">
         <v>1780000</v>
       </c>
-      <c r="Q34" s="20">
+      <c r="Q34" s="5">
         <f t="shared" si="0"/>
         <v>1780</v>
       </c>
-      <c r="R34" s="21" t="s">
+      <c r="R34" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S34" s="18" t="s">
+      <c r="S34" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="22" t="s">
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="W34" s="22"/>
-      <c r="X34" s="22" t="s">
+      <c r="W34" s="17"/>
+      <c r="X34" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="Y34" s="22" t="s">
+      <c r="Y34" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="Z34" s="22" t="s">
+      <c r="Z34" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="AA34" s="22" t="s">
+      <c r="AA34" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB34" s="22" t="s">
-        <v>623</v>
-      </c>
-      <c r="AC34" s="22"/>
-    </row>
-    <row r="35" spans="1:29" ht="27">
-      <c r="A35" s="16">
+      <c r="AB34" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="AC34" s="17"/>
+    </row>
+    <row r="35" spans="1:29">
+      <c r="A35" s="20">
         <v>34</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="4">
         <v>44753</v>
       </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19">
+      <c r="I35" s="4"/>
+      <c r="J35" s="4">
         <v>44753</v>
       </c>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="17">
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="2">
         <v>2022</v>
       </c>
-      <c r="O35" s="17">
-        <v>1</v>
-      </c>
-      <c r="P35" s="20">
+      <c r="O35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35" s="5">
         <v>1780000</v>
       </c>
-      <c r="Q35" s="20">
+      <c r="Q35" s="5">
         <f t="shared" si="0"/>
         <v>1780</v>
       </c>
-      <c r="R35" s="21" t="s">
+      <c r="R35" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S35" s="18" t="s">
+      <c r="S35" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="22" t="s">
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="W35" s="22"/>
-      <c r="X35" s="22" t="s">
+      <c r="W35" s="17"/>
+      <c r="X35" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="Y35" s="22" t="s">
+      <c r="Y35" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="Z35" s="22" t="s">
+      <c r="Z35" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="AA35" s="22" t="s">
+      <c r="AA35" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB35" s="22" t="s">
-        <v>623</v>
-      </c>
-      <c r="AC35" s="22"/>
-    </row>
-    <row r="36" spans="1:29" ht="81">
-      <c r="A36" s="16">
+      <c r="AB35" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="AC35" s="17"/>
+    </row>
+    <row r="36" spans="1:29">
+      <c r="A36" s="20">
         <v>35</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="4">
         <v>44761</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="4">
         <v>44761</v>
       </c>
-      <c r="J36" s="19">
+      <c r="J36" s="4">
         <v>44761</v>
       </c>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="17">
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="2">
         <v>2022</v>
       </c>
-      <c r="O36" s="17">
-        <v>1</v>
-      </c>
-      <c r="P36" s="20">
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36" s="5">
         <v>161442760</v>
       </c>
-      <c r="Q36" s="20">
+      <c r="Q36" s="5">
         <f t="shared" si="0"/>
         <v>161443</v>
       </c>
-      <c r="R36" s="21" t="s">
+      <c r="R36" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S36" s="18" t="s">
+      <c r="S36" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="T36" s="18" t="s">
+      <c r="T36" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="U36" s="18" t="s">
+      <c r="U36" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="V36" s="22" t="s">
+      <c r="V36" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="W36" s="22" t="s">
+      <c r="W36" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="X36" s="22" t="s">
+      <c r="X36" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="Y36" s="22" t="s">
+      <c r="Y36" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="Z36" s="22" t="s">
+      <c r="Z36" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="AA36" s="22" t="s">
+      <c r="AA36" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB36" s="22" t="s">
-        <v>624</v>
-      </c>
-      <c r="AC36" s="22"/>
-    </row>
-    <row r="37" spans="1:29" ht="27">
-      <c r="A37" s="16">
+      <c r="AB36" s="17" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC36" s="17"/>
+    </row>
+    <row r="37" spans="1:29">
+      <c r="A37" s="20">
         <v>36</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="4">
         <v>43647</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="4">
         <v>43647</v>
       </c>
-      <c r="J37" s="19">
+      <c r="J37" s="4">
         <v>43647</v>
       </c>
-      <c r="K37" s="19"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="19">
+      <c r="K37" s="4"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="4">
         <v>44853</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N37" s="2">
         <v>2019</v>
       </c>
-      <c r="O37" s="17">
-        <v>1</v>
-      </c>
-      <c r="P37" s="20">
+      <c r="O37" s="2">
+        <v>1</v>
+      </c>
+      <c r="P37" s="5">
         <v>38708980</v>
       </c>
-      <c r="Q37" s="20">
+      <c r="Q37" s="5">
         <f t="shared" si="0"/>
         <v>38709</v>
       </c>
-      <c r="R37" s="21" t="s">
+      <c r="R37" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S37" s="18" t="s">
+      <c r="S37" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="T37" s="18" t="s">
+      <c r="T37" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="U37" s="18"/>
-      <c r="V37" s="22" t="s">
+      <c r="U37" s="3"/>
+      <c r="V37" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="W37" s="22"/>
-      <c r="X37" s="22" t="s">
+      <c r="W37" s="17"/>
+      <c r="X37" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="Y37" s="22" t="s">
+      <c r="Y37" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="Z37" s="22" t="s">
+      <c r="Z37" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="AA37" s="22" t="s">
+      <c r="AA37" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB37" s="22" t="s">
-        <v>625</v>
-      </c>
-      <c r="AC37" s="22"/>
+      <c r="AB37" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="AC37" s="17"/>
     </row>
     <row r="38" spans="1:29">
-      <c r="A38" s="16">
+      <c r="A38" s="20">
         <v>37</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="4">
         <v>44964</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="4">
         <v>44964</v>
       </c>
-      <c r="J38" s="19">
+      <c r="J38" s="4">
         <v>44964</v>
       </c>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="17">
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="2">
         <v>2023</v>
       </c>
-      <c r="O38" s="17">
-        <v>1</v>
-      </c>
-      <c r="P38" s="20">
+      <c r="O38" s="2">
+        <v>1</v>
+      </c>
+      <c r="P38" s="5">
         <v>6996000</v>
       </c>
-      <c r="Q38" s="20">
+      <c r="Q38" s="5">
         <f t="shared" si="0"/>
         <v>6996</v>
       </c>
-      <c r="R38" s="21" t="s">
+      <c r="R38" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S38" s="18" t="s">
+      <c r="S38" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="22"/>
-      <c r="W38" s="22"/>
-      <c r="X38" s="22"/>
-      <c r="Y38" s="22"/>
-      <c r="Z38" s="22"/>
-      <c r="AA38" s="22" t="s">
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB38" s="22"/>
-      <c r="AC38" s="22"/>
-    </row>
-    <row r="39" spans="1:29" ht="40.5">
-      <c r="A39" s="16">
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="17"/>
+    </row>
+    <row r="39" spans="1:29">
+      <c r="A39" s="20">
         <v>38</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="4">
         <v>45042</v>
       </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19">
+      <c r="I39" s="4"/>
+      <c r="J39" s="4">
         <v>45042</v>
       </c>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="17">
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="2">
         <v>2023</v>
       </c>
-      <c r="O39" s="17">
-        <v>1</v>
-      </c>
-      <c r="P39" s="20">
+      <c r="O39" s="2">
+        <v>1</v>
+      </c>
+      <c r="P39" s="5">
         <v>3740000</v>
       </c>
-      <c r="Q39" s="20">
+      <c r="Q39" s="5">
         <f t="shared" si="0"/>
         <v>3740</v>
       </c>
-      <c r="R39" s="21" t="s">
+      <c r="R39" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S39" s="18" t="s">
+      <c r="S39" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="22"/>
-      <c r="W39" s="22"/>
-      <c r="X39" s="22"/>
-      <c r="Y39" s="22"/>
-      <c r="Z39" s="22"/>
-      <c r="AA39" s="22" t="s">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="17"/>
+      <c r="AA39" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB39" s="22"/>
-      <c r="AC39" s="22"/>
-    </row>
-    <row r="40" spans="1:29" ht="94.5">
-      <c r="A40" s="16">
+      <c r="AB39" s="17"/>
+      <c r="AC39" s="17"/>
+    </row>
+    <row r="40" spans="1:29">
+      <c r="A40" s="20">
         <v>39</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="4">
         <v>45097</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="4">
         <v>45097</v>
       </c>
-      <c r="J40" s="19">
+      <c r="J40" s="4">
         <v>45097</v>
       </c>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="17">
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="2">
         <v>2023</v>
       </c>
-      <c r="O40" s="17">
-        <v>1</v>
-      </c>
-      <c r="P40" s="20">
+      <c r="O40" s="2">
+        <v>1</v>
+      </c>
+      <c r="P40" s="5">
         <v>86754320</v>
       </c>
-      <c r="Q40" s="20">
+      <c r="Q40" s="5">
         <f t="shared" si="0"/>
         <v>86754</v>
       </c>
-      <c r="R40" s="21" t="s">
+      <c r="R40" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S40" s="18" t="s">
+      <c r="S40" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="22" t="s">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="W40" s="22" t="s">
+      <c r="W40" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="X40" s="22" t="s">
+      <c r="X40" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="Y40" s="22" t="s">
+      <c r="Y40" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="Z40" s="22" t="s">
+      <c r="Z40" s="17" t="s">
         <v>445</v>
       </c>
-      <c r="AA40" s="22" t="s">
+      <c r="AA40" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB40" s="22" t="s">
-        <v>626</v>
-      </c>
-      <c r="AC40" s="22" t="s">
+      <c r="AB40" s="17" t="s">
+        <v>596</v>
+      </c>
+      <c r="AC40" s="17" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="162">
-      <c r="A41" s="16">
+    <row r="41" spans="1:29">
+      <c r="A41" s="20">
         <v>40</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="H41" s="19">
+      <c r="H41" s="4">
         <v>45125</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="4">
         <v>45125</v>
       </c>
-      <c r="J41" s="19">
+      <c r="J41" s="4">
         <v>45125</v>
       </c>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="17">
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="2">
         <v>2023</v>
       </c>
-      <c r="O41" s="17">
-        <v>1</v>
-      </c>
-      <c r="P41" s="20">
+      <c r="O41" s="2">
+        <v>1</v>
+      </c>
+      <c r="P41" s="5">
         <v>101694480</v>
       </c>
-      <c r="Q41" s="20">
+      <c r="Q41" s="5">
         <f t="shared" si="0"/>
         <v>101694</v>
       </c>
-      <c r="R41" s="21" t="s">
+      <c r="R41" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S41" s="18" t="s">
+      <c r="S41" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="22" t="s">
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="W41" s="22" t="s">
+      <c r="W41" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="X41" s="22" t="s">
+      <c r="X41" s="17" t="s">
         <v>446</v>
       </c>
-      <c r="Y41" s="22" t="s">
+      <c r="Y41" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="Z41" s="22" t="s">
+      <c r="Z41" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="AA41" s="22" t="s">
+      <c r="AA41" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB41" s="22" t="s">
-        <v>627</v>
-      </c>
-      <c r="AC41" s="22"/>
-    </row>
-    <row r="42" spans="1:29" ht="27">
-      <c r="A42" s="16">
+      <c r="AB41" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="AC41" s="17"/>
+    </row>
+    <row r="42" spans="1:29">
+      <c r="A42" s="20">
         <v>41</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="H42" s="19">
+      <c r="H42" s="4">
         <v>44756</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="4">
         <v>44756</v>
       </c>
-      <c r="J42" s="19">
+      <c r="J42" s="4">
         <v>44756</v>
       </c>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="17">
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="2">
         <v>2022</v>
       </c>
-      <c r="O42" s="17">
-        <v>1</v>
-      </c>
-      <c r="P42" s="20">
+      <c r="O42" s="2">
+        <v>1</v>
+      </c>
+      <c r="P42" s="5">
         <v>5156320</v>
       </c>
-      <c r="Q42" s="20">
+      <c r="Q42" s="5">
         <f t="shared" si="0"/>
         <v>5156</v>
       </c>
-      <c r="R42" s="21" t="s">
+      <c r="R42" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S42" s="18" t="s">
+      <c r="S42" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="22" t="s">
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="W42" s="22"/>
-      <c r="X42" s="22" t="s">
+      <c r="W42" s="17"/>
+      <c r="X42" s="17" t="s">
         <v>449</v>
       </c>
-      <c r="Y42" s="22" t="s">
+      <c r="Y42" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="Z42" s="22" t="s">
+      <c r="Z42" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="AA42" s="22" t="s">
+      <c r="AA42" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB42" s="22" t="s">
-        <v>628</v>
-      </c>
-      <c r="AC42" s="22"/>
-    </row>
-    <row r="43" spans="1:29" ht="27">
-      <c r="A43" s="16">
+      <c r="AB42" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="AC42" s="17"/>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="A43" s="20">
         <v>42</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G43" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="H43" s="19">
+      <c r="H43" s="4">
         <v>44756</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="4">
         <v>44756</v>
       </c>
-      <c r="J43" s="19">
+      <c r="J43" s="4">
         <v>44756</v>
       </c>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="17">
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="2">
         <v>2022</v>
       </c>
-      <c r="O43" s="17">
-        <v>1</v>
-      </c>
-      <c r="P43" s="20">
+      <c r="O43" s="2">
+        <v>1</v>
+      </c>
+      <c r="P43" s="5">
         <v>5156310</v>
       </c>
-      <c r="Q43" s="20">
+      <c r="Q43" s="5">
         <f t="shared" si="0"/>
         <v>5156</v>
       </c>
-      <c r="R43" s="21" t="s">
+      <c r="R43" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S43" s="18" t="s">
+      <c r="S43" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="22" t="s">
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="W43" s="22"/>
-      <c r="X43" s="22" t="s">
+      <c r="W43" s="17"/>
+      <c r="X43" s="17" t="s">
         <v>449</v>
       </c>
-      <c r="Y43" s="22" t="s">
+      <c r="Y43" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="Z43" s="22" t="s">
+      <c r="Z43" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="AA43" s="22" t="s">
+      <c r="AA43" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB43" s="22" t="s">
-        <v>628</v>
-      </c>
-      <c r="AC43" s="22"/>
-    </row>
-    <row r="44" spans="1:29" ht="54">
-      <c r="A44" s="16">
+      <c r="AB43" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="AC43" s="17"/>
+    </row>
+    <row r="44" spans="1:29">
+      <c r="A44" s="20">
         <v>43</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G44" s="18" t="s">
+      <c r="G44" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="4">
         <v>45737</v>
       </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19">
+      <c r="I44" s="4"/>
+      <c r="J44" s="4">
         <v>45737</v>
       </c>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="17">
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="2">
         <v>2025</v>
       </c>
-      <c r="O44" s="17">
-        <v>1</v>
-      </c>
-      <c r="P44" s="20">
+      <c r="O44" s="2">
+        <v>1</v>
+      </c>
+      <c r="P44" s="5">
         <v>2099025</v>
       </c>
-      <c r="Q44" s="20">
+      <c r="Q44" s="5">
         <f t="shared" si="0"/>
         <v>2099</v>
       </c>
-      <c r="R44" s="21" t="s">
+      <c r="R44" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S44" s="18" t="s">
+      <c r="S44" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="T44" s="18"/>
-      <c r="U44" s="18"/>
-      <c r="V44" s="22" t="s">
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="W44" s="22" t="s">
+      <c r="W44" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="X44" s="22" t="s">
+      <c r="X44" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="Y44" s="22" t="s">
+      <c r="Y44" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="Z44" s="22" t="s">
+      <c r="Z44" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="AA44" s="22" t="s">
+      <c r="AA44" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB44" s="22" t="s">
-        <v>629</v>
-      </c>
-      <c r="AC44" s="22"/>
-    </row>
-    <row r="45" spans="1:29" ht="54">
-      <c r="A45" s="16">
+      <c r="AB44" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC44" s="17"/>
+    </row>
+    <row r="45" spans="1:29">
+      <c r="A45" s="20">
         <v>44</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="H45" s="19">
+      <c r="H45" s="4">
         <v>45737</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19">
+      <c r="I45" s="4"/>
+      <c r="J45" s="4">
         <v>45737</v>
       </c>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="17">
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="2">
         <v>2025</v>
       </c>
-      <c r="O45" s="17">
-        <v>1</v>
-      </c>
-      <c r="P45" s="20">
+      <c r="O45" s="2">
+        <v>1</v>
+      </c>
+      <c r="P45" s="5">
         <v>2099025</v>
       </c>
-      <c r="Q45" s="20">
+      <c r="Q45" s="5">
         <f t="shared" si="0"/>
         <v>2099</v>
       </c>
-      <c r="R45" s="21" t="s">
+      <c r="R45" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S45" s="18" t="s">
+      <c r="S45" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="22" t="s">
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="W45" s="22" t="s">
+      <c r="W45" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="X45" s="22" t="s">
+      <c r="X45" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="Y45" s="22" t="s">
+      <c r="Y45" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="Z45" s="22" t="s">
+      <c r="Z45" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="AA45" s="22" t="s">
+      <c r="AA45" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB45" s="22" t="s">
-        <v>629</v>
-      </c>
-      <c r="AC45" s="22"/>
-    </row>
-    <row r="46" spans="1:29" ht="67.5">
-      <c r="A46" s="16">
+      <c r="AB45" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="AC45" s="17"/>
+    </row>
+    <row r="46" spans="1:29">
+      <c r="A46" s="20">
         <v>45</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G46" s="18" t="s">
+      <c r="G46" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="4">
         <v>45792</v>
       </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19">
+      <c r="I46" s="4"/>
+      <c r="J46" s="4">
         <v>45792</v>
       </c>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="17">
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="2">
         <v>2025</v>
       </c>
-      <c r="O46" s="17">
-        <v>1</v>
-      </c>
-      <c r="P46" s="20">
+      <c r="O46" s="2">
+        <v>1</v>
+      </c>
+      <c r="P46" s="5">
         <v>4840000</v>
       </c>
-      <c r="Q46" s="20">
+      <c r="Q46" s="5">
         <f t="shared" si="0"/>
         <v>4840</v>
       </c>
-      <c r="R46" s="21" t="s">
+      <c r="R46" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S46" s="22" t="s">
+      <c r="S46" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="T46" s="18" t="s">
+      <c r="T46" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="U46" s="18"/>
-      <c r="V46" s="22" t="s">
+      <c r="U46" s="3"/>
+      <c r="V46" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="W46" s="22" t="s">
+      <c r="W46" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="X46" s="22" t="s">
+      <c r="X46" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="Y46" s="22" t="s">
+      <c r="Y46" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="Z46" s="22" t="s">
+      <c r="Z46" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="AA46" s="22" t="s">
+      <c r="AA46" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB46" s="22" t="s">
-        <v>630</v>
-      </c>
-      <c r="AC46" s="22"/>
-    </row>
-    <row r="47" spans="1:29" ht="81">
-      <c r="A47" s="16">
+      <c r="AB46" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="AC46" s="17"/>
+    </row>
+    <row r="47" spans="1:29">
+      <c r="A47" s="20">
         <v>46</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="H47" s="19">
+      <c r="H47" s="4">
         <v>45866</v>
       </c>
-      <c r="I47" s="19">
+      <c r="I47" s="4">
         <v>45866</v>
       </c>
-      <c r="J47" s="19">
+      <c r="J47" s="4">
         <v>45866</v>
       </c>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="17">
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="2">
         <v>2025</v>
       </c>
-      <c r="O47" s="17">
-        <v>1</v>
-      </c>
-      <c r="P47" s="20">
+      <c r="O47" s="2">
+        <v>1</v>
+      </c>
+      <c r="P47" s="5">
         <v>40480000</v>
       </c>
-      <c r="Q47" s="20">
+      <c r="Q47" s="5">
         <f t="shared" si="0"/>
         <v>40480</v>
       </c>
-      <c r="R47" s="21" t="s">
+      <c r="R47" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S47" s="22" t="s">
+      <c r="S47" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="T47" s="18" t="s">
+      <c r="T47" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="U47" s="18"/>
-      <c r="V47" s="22" t="s">
+      <c r="U47" s="3"/>
+      <c r="V47" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="W47" s="22" t="s">
+      <c r="W47" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="X47" s="22" t="s">
+      <c r="X47" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="Y47" s="22" t="s">
+      <c r="Y47" s="17" t="s">
         <v>458</v>
       </c>
-      <c r="Z47" s="22" t="s">
+      <c r="Z47" s="17" t="s">
         <v>459</v>
       </c>
-      <c r="AA47" s="22" t="s">
+      <c r="AA47" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB47" s="22" t="s">
-        <v>631</v>
-      </c>
-      <c r="AC47" s="22"/>
-    </row>
-    <row r="48" spans="1:29" ht="108.75">
-      <c r="A48" s="16">
+      <c r="AB47" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="AC47" s="17"/>
+    </row>
+    <row r="48" spans="1:29">
+      <c r="A48" s="20">
         <v>47</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F48" s="18" t="s">
+      <c r="F48" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G48" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H48" s="19">
+      <c r="H48" s="4">
         <v>45958</v>
       </c>
-      <c r="I48" s="19">
+      <c r="I48" s="4">
         <v>45859</v>
       </c>
-      <c r="J48" s="19">
+      <c r="J48" s="4">
         <v>45859</v>
       </c>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="17">
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="2">
         <v>2025</v>
       </c>
-      <c r="O48" s="17">
-        <v>1</v>
-      </c>
-      <c r="P48" s="20">
+      <c r="O48" s="2">
+        <v>1</v>
+      </c>
+      <c r="P48" s="5">
         <v>74988220</v>
       </c>
-      <c r="Q48" s="20">
+      <c r="Q48" s="5">
         <f t="shared" si="0"/>
         <v>74988</v>
       </c>
-      <c r="R48" s="21" t="s">
+      <c r="R48" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="S48" s="18" t="s">
+      <c r="S48" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
-      <c r="V48" s="22" t="s">
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="W48" s="22" t="s">
+      <c r="W48" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="X48" s="22" t="s">
+      <c r="X48" s="17" t="s">
         <v>460</v>
       </c>
-      <c r="Y48" s="22" t="s">
+      <c r="Y48" s="17" t="s">
         <v>461</v>
       </c>
-      <c r="Z48" s="22" t="s">
+      <c r="Z48" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="AA48" s="22" t="s">
+      <c r="AA48" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="AB48" s="22" t="s">
-        <v>632</v>
-      </c>
-      <c r="AC48" s="22"/>
+      <c r="AB48" s="17" t="s">
+        <v>597</v>
+      </c>
+      <c r="AC48" s="17"/>
+    </row>
+    <row r="49" spans="1:28" s="32" customFormat="1">
+      <c r="A49" s="24">
+        <v>48</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>588</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>598</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>598</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>589</v>
+      </c>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="27">
+        <v>41813</v>
+      </c>
+      <c r="I49" s="27">
+        <v>41813</v>
+      </c>
+      <c r="J49" s="27">
+        <v>41813</v>
+      </c>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="28">
+        <v>2014</v>
+      </c>
+      <c r="O49" s="28">
+        <v>1</v>
+      </c>
+      <c r="P49" s="29">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="29">
+        <f t="shared" ref="Q49" si="1">ROUND(P49/1000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="S49" s="26" t="s">
+        <v>589</v>
+      </c>
+      <c r="T49" s="26" t="s">
+        <v>590</v>
+      </c>
+      <c r="U49" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="V49" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="W49" s="31" t="s">
+        <v>329</v>
+      </c>
+      <c r="X49" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="Y49" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="Z49" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="AA49" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="AB49" s="32" t="s">
+        <v>591</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6596,133 +6442,133 @@
   <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="6" width="9.140625" style="9"/>
-    <col min="7" max="10" width="11.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="9"/>
-    <col min="13" max="14" width="9.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="6" width="9.140625" style="7"/>
+    <col min="7" max="10" width="11.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="7"/>
+    <col min="13" max="14" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>38877</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>38877</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>38877</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>45292</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="3">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="2">
         <v>2006</v>
       </c>
-      <c r="N2" s="3">
-        <v>1</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="N2" s="2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
         <v>35373600</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="5">
         <f>ROUND(O2/1000,0)</f>
         <v>35374</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="T2" s="4"/>
+      <c r="T2" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6732,1657 +6578,1210 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6DCEEE-C7F8-4842-933D-899B956166E0}">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.5703125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="18.5703125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
-        <v>603</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>633</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="A1" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>635</v>
+      <c r="D1" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="D3" s="13">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="13">
+        <v>3</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="13">
+        <v>4</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="13">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="13">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="D8" s="13">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="13">
+        <v>4</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="13">
+        <v>5</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="D10" s="13">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="B11" s="13">
+        <v>1</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="D11" s="13">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="B12" s="13">
+        <v>2</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="D13" s="13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D14" s="13">
+        <v>16</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="13">
+        <v>3</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="D15" s="13">
+        <v>10</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="13">
+        <v>1</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="13">
+        <v>2</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D17" s="13">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="D18" s="13">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="13">
+        <v>2</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="D19" s="13">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="13">
+        <v>3</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="D20" s="13">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="13">
+        <v>1</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D21" s="13">
+        <v>2</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="13">
+        <v>2</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="D22" s="13">
+        <v>2</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="13">
+        <v>1</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="13">
+        <v>2</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="13">
+        <v>3</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="13">
+        <v>4</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="13">
+        <v>1</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="D27" s="13">
+        <v>1</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="13">
+        <v>2</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="D28" s="13">
+        <v>1</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="13">
+        <v>3</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="D29" s="13">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="13">
+        <v>4</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="D30" s="13">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="13">
+        <v>1</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="D31" s="13">
+        <v>1</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D32" s="13">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="13">
+        <v>1</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="13">
+        <v>2</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="D34" s="13">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="13">
+        <v>1</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="D35" s="13">
+        <v>1</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="13">
+        <v>2</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="13">
+        <v>3</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="13">
+        <v>4</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D38" s="13">
+        <v>1</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="13">
+        <v>5</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="D39" s="13">
+        <v>1</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="13">
+        <v>1</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="D40" s="13">
+        <v>1</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="13">
+        <v>2</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D41" s="13">
+        <v>1</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="13">
+        <v>3</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="D42" s="13">
+        <v>1</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="13">
+        <v>1</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="13">
+        <v>1</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="D44" s="13">
+        <v>1</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="13">
+        <v>1</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="D45" s="13">
+        <v>1</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="13">
+        <v>2</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="D46" s="13">
+        <v>1</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" s="13">
+        <v>3</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="D47" s="13">
+        <v>1</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" s="13">
+        <v>4</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="D48" s="13">
+        <v>1</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" s="13">
+        <v>5</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="D49" s="13">
+        <v>1</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" s="13">
+        <v>1</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="D50" s="13">
+        <v>1</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B51" s="13">
+        <v>2</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D51" s="13">
+        <v>1</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="13">
+        <v>3</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="D52" s="13">
+        <v>1</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="13">
+        <v>4</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="D53" s="13">
+        <v>2</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="13">
+        <v>5</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="D54" s="13">
+        <v>1</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="13">
+        <v>1</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D55" s="13">
+        <v>2</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B56" s="13">
+        <v>1</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="D56" s="13">
+        <v>2</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D57" s="13">
+        <v>1</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="D58" s="13">
+        <v>1</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="13">
+        <v>2</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="D59" s="13">
+        <v>1</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" s="13">
+        <v>3</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="D60" s="13">
+        <v>1</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="13">
+        <v>4</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="D61" s="13">
+        <v>1</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" s="13">
+        <v>5</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="D62" s="13">
+        <v>4</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B63" s="13">
+        <v>6</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="D63" s="13">
+        <v>12</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B64" s="13">
+        <v>7</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="D64" s="13">
+        <v>1</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="13">
+        <v>8</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="D65" s="13">
+        <v>1</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" s="13">
+        <v>1</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="D66" s="13">
+        <v>1</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67" s="13">
+        <v>2</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="D67" s="13">
+        <v>2</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="13">
+        <v>3</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="D68" s="13">
+        <v>1</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" s="13">
+        <v>4</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="D69" s="13">
+        <v>1</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B70" s="13">
+        <v>5</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D70" s="13">
+        <v>1</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B71" s="13">
+        <v>6</v>
+      </c>
+      <c r="C71" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>601</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>600</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>598</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
-        <v>595</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>597</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="27">
-      <c r="A5" s="11" t="s">
-        <v>595</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>596</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="27">
-      <c r="A6" s="11" t="s">
-        <v>595</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="27">
-      <c r="A7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>593</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="27">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="27">
-      <c r="A9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>591</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>589</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="11" t="s">
-        <v>582</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="11" t="s">
-        <v>582</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>585</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="11" t="s">
-        <v>582</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="11" t="s">
-        <v>582</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>583</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="11" t="s">
-        <v>582</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>581</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>580</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>578</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>577</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>576</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>574</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>573</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>569</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>567</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>561</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>556</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>500</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>500</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>500</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>553</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="E46" s="11" t="s">
+      <c r="D71" s="13">
+        <v>1</v>
+      </c>
+      <c r="E71" s="12" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>548</v>
-      </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>542</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>535</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>533</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>524</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>523</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>522</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="27">
-      <c r="A77" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>521</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>520</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="27">
-      <c r="A80" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>515</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="D83" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="D85" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>510</v>
-      </c>
-      <c r="D86" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>509</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>508</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>506</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>505</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>504</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>503</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>498</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>493</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E96" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E97" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="E98" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E98" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:E71" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
